--- a/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>PUK</t>
   </si>
@@ -656,359 +656,383 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3146500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3146500</v>
+      </c>
+      <c r="F8" s="3">
         <v>4008000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4008000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3205500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3205500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3373500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3373500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2662500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2662500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2820500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2809500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2709500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2709500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2797500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>42311000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U8" s="3">
         <v>41197000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>52539000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>35845000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>16019000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>43466000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>42924000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>36301000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>45947800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>20902900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>33287100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>38844000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2264000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2264000</v>
+      </c>
+      <c r="F9" s="3">
         <v>2185000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2185000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2043000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2043000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2087500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2087500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1945000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1945000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1856000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1856000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1786000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1786000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1735500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>647000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1433000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2068000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2109000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>6103000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>3186000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1792000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1920000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1987000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2197800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2210800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2080500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>4498200</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>882500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>882500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1823000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1823000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1162500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1162500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1286000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1286000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>717500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>717500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>964500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>953500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>923500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>923500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1062000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>41664000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U10" s="3">
         <v>39129000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>50430000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>29742000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>12833000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>41674000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>41004000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>34314000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>43750000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>18692100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>31206600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>34345800</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1038,8 +1062,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1121,8 +1147,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1204,165 +1236,177 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F14" s="3">
         <v>-8000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-8000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>8000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>8000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>34500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>34500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>11000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>30000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>159000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-17000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>182000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>570000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-162000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>238000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>121500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>121500</v>
+      </c>
+      <c r="F15" s="3">
         <v>134500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>134500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>117000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>117000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>112000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>112000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>102500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>102500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>106500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>106500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>108000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>108000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>169000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>77000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>109000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3">
         <v>107000</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
@@ -1370,8 +1414,14 @@
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1398,174 +1448,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2264000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2264000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2185000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2185000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2043000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2043000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2087500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2087500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1945000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1945000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1856000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1856000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1786000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1786000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1735500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>40297000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>-6757000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>40471000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>51224000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>32167000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>14313000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>41957000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>41014000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>34595000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>44982000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>19189000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>30714100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>37257300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>882500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>882500</v>
+      </c>
+      <c r="F18" s="3">
         <v>1823000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1823000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1162500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1162500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1286000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1286000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>717500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>717500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>964500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>953500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>923500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>923500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1062000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>2014000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U18" s="3">
         <v>726000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1315000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3678000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1706000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1509000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1910000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1706000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>965700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1713900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>2573000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1586700</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1595,174 +1659,188 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>235500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>235500</v>
+      </c>
+      <c r="F20" s="3">
         <v>76000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>76000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>257500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>257500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-124500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-124500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>387500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>387500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>250000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>250000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>259500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>259500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>480000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>384000</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U20" s="3">
         <v>260000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>137000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>319000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>82000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>182000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>120000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>96000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>111200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>151300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>100100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>205400</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>768500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>768500</v>
+      </c>
+      <c r="F21" s="3">
         <v>1881500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1881500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1022000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1022000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1522500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1522500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>432500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>432500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>821000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>810000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>772000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>772000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>751000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2366000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3">
         <v>999000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1559000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3">
         <v>1822000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1687000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2090000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1811000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1173900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1889900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>2745500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1792200</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1773,245 +1851,263 @@
         <v>48000</v>
       </c>
       <c r="F22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="H22" s="3">
         <v>43500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>43500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>43000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>43000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>42500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>42500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>189000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>189000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>42500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>42500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>180000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>153000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>163000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>223000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>293000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>547000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>189000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>209000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>216000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>191000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>218500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>213900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>194900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>225200</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>593000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>593000</v>
+      </c>
+      <c r="F23" s="3">
         <v>1707000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1707000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>853500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>853500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1366500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1366500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>253000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>253000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>514500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>514500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>621500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>621500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>402000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>2245000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>663000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>763000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1159000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3450000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1599000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1482000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1814000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1611000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>858400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1651300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2478200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1567000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>95500</v>
+      </c>
+      <c r="F24" s="3">
         <v>327000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>327000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>174000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>174000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>250000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>250000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>162000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>162000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>132000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>132000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>148000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>148000</v>
       </c>
       <c r="P24" s="3">
         <v>148000</v>
       </c>
       <c r="Q24" s="3">
+        <v>148000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>148000</v>
+      </c>
+      <c r="S24" s="3">
         <v>311000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>129000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-32000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>569000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>326000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>152000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>309000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>377000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-29700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>163000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>584700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2093,174 +2189,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>497500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>497500</v>
+      </c>
+      <c r="F26" s="3">
         <v>1380000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1380000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>679500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>679500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1116500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1116500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>91000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>91000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>382500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>382500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>473500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>473500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>254000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1934000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>534000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>795000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1158000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2881000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1273000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1330000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1505000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>888200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1488200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1893500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>477000</v>
+      </c>
+      <c r="F27" s="3">
         <v>1347000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1347000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>642000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>642000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1082500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1082500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>60000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>60000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>378500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>378500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>472000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>472000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>250500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1946000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>512000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>792000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1152000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2877000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1272000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1329000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1505000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>888200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1488200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1893500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2342,8 +2456,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2387,32 +2507,32 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-340000</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-1996000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>1480000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>1142000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>83000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>-445000</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2425,8 +2545,14 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2508,8 +2634,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2591,174 +2723,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-235500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-235500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-76000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-76000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-257500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-257500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>124500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>124500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-387500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-387500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-250000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-250000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-259500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-259500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-480000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-384000</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U32" s="3">
         <v>-260000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-137000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-319000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-82000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-182000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-96000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-111200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-151300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-100100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-205400</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>477000</v>
+      </c>
+      <c r="F33" s="3">
         <v>1347000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1347000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>642000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>642000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1082500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1082500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>60000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>60000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>378500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>378500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>472000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>472000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>250500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1606000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>512000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1204000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2632000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>4019000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1355000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>884000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1505000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>888200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1488200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1893500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2840,179 +2990,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>477000</v>
+      </c>
+      <c r="F35" s="3">
         <v>1347000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1347000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>642000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>642000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1082500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1082500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>60000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>60000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>378500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>378500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>472000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>472000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>250500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1606000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>512000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1204000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2632000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>4019000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1355000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>884000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1505000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>888200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1488200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1893500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3042,8 +3210,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3073,91 +3243,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5889000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5889000</v>
+      </c>
+      <c r="F41" s="3">
         <v>3851000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3851000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5636000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5636000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2445000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2445000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5978000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5978000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4751000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4751000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5920000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5920000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5514000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>7431000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>7785000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>6609000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>6119000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>27051000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>8312000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>20400000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>19024000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>9843000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>11027700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>9676700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>10926700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>8439300</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3239,91 +3417,103 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3631000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3631000</v>
+      </c>
+      <c r="F43" s="3">
         <v>2710000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2710000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4081000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4081000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2686000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2686000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3596000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3596000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2375000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2375000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2220000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2220000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2120000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3171000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2729000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2054000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2159000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>7990000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3120000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>5681000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>6610000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2872000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>4531300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2549900</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3366,11 +3556,11 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3405,56 +3595,62 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5492000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5492000</v>
+      </c>
+      <c r="F45" s="3">
         <v>5098000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5098000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>6116000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>6116000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4983000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4983000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4727000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4727000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5284000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>5284000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3498000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3498000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3408000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
@@ -3488,56 +3684,62 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15012000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15012000</v>
+      </c>
+      <c r="F46" s="3">
         <v>15514000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>15514000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>15833000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>15833000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13441000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>13441000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14301000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>14301000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12410000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>12410000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>11638000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>11638000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>11042000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
       <c r="S46" s="3">
         <v>0</v>
       </c>
@@ -3571,257 +3773,281 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>203106000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>203106000</v>
+      </c>
+      <c r="F47" s="3">
         <v>190618000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>190618000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>177234000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>177234000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>162684000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>162684000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>154718000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>154718000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>155627000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>155627000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>148072000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>148072000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>143229000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>400592000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>377884000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>379715000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>639141000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>913733000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>404637000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>802481000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>796888000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>388381000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>476271200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>424114700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>434640800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>427702600</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>529000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>529000</v>
+      </c>
+      <c r="F48" s="3">
         <v>530000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>530000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>537000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>537000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>417000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>417000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>390000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>390000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>374000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>374000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>396000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>396000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>437000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>916000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>987000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1090000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1798000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>24624000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>18556000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>33101000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>30513000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>15389000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>19591200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>19067700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>18755000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>18095300</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4614000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4614000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4860000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4860000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4828000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4828000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4672000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4672000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4577000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4577000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4882000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4882000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4565000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4565000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>4774000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1031000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1008000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1036000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>723000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>4193000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1769000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1627000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1615000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1680000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2226200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2214700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2166100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2171400</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3903,8 +4129,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3986,16 +4218,22 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E52" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F52" s="3">
         <v>3000</v>
@@ -4016,61 +4254,67 @@
         <v>3000</v>
       </c>
       <c r="L52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N52" s="3">
         <v>39000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>39000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>45000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>45000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>37000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4858000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4259000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>4075000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>284138000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>29949000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>14459000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>5330000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>8276000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>6027000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>4914000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3678200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>3713300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>4726000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4152,91 +4396,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>223679000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>223679000</v>
+      </c>
+      <c r="F54" s="3">
         <v>212195000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>212195000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>199119000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>199119000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>181876000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>181876000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>174687000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>174687000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>174066000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>174066000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>165458000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>165458000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>160249000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>516097000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>463165000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>454214000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>705945000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>647810000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>501170000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>493941000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>481130000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>470498000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>567962500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>504748400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>497616300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>486164100</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4266,8 +4522,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4297,56 +4555,58 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>743000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>743000</v>
+      </c>
+      <c r="F57" s="3">
         <v>640000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>640000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>510000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>510000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>536000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>536000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1379000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1379000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1151000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1151000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>950000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>950000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1175000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
@@ -4380,82 +4640,88 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1361000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1361000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1165000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1165000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>883000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>883000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1236000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1236000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1491000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1491000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1146000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1146000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1566000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>501000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>506000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>549000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>841000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>716000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -4463,139 +4729,151 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4705000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4705000</v>
+      </c>
+      <c r="F59" s="3">
         <v>4118000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4118000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3804000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3804000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>4778000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4778000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3816000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3816000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3224000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3224000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3397000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3397000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5402000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>477515000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>429139000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>419599000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>393980000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>830364000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>453226000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>816205000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>866408000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>369166000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>507721400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>399974500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>448806800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>360479200</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9881000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9881000</v>
+      </c>
+      <c r="F60" s="3">
         <v>6485000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6485000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10486000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>10486000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6470000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6470000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9639000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>9639000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6145000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6145000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7571000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7571000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>8402000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
       <c r="S60" s="3">
         <v>0</v>
       </c>
@@ -4629,174 +4907,192 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4790000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4790000</v>
+      </c>
+      <c r="F61" s="3">
         <v>4674000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4674000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4826000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4826000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4111000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4111000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4231000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4231000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4099000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4099000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4222000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4222000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4092000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8576000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>8223000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7669000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>11004000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>15334000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>11570000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>11787000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>12046000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>10452000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>13166000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>10829700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>11157200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>10086600</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>186561000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>186561000</v>
+      </c>
+      <c r="F62" s="3">
         <v>177846000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>177846000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>162591000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>162591000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>151107000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>151107000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>142242000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>142242000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>144589000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>144589000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>135140000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>135140000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>129718000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>6075000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>5278000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>5237000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>277443000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>33150000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>16420000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>9392000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>11366000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>6761000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>6938500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>5195100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>5695100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>5650300</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4878,8 +5174,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4961,8 +5263,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5044,91 +5352,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>203056000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>203056000</v>
+      </c>
+      <c r="F66" s="3">
         <v>190835000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>190835000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>179675000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>179675000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>163202000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>163202000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>157451000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>157451000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>156083000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>156083000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>148147000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>148147000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>143351000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>495219000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>444055000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>434737000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>680908000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>625842000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>485288000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>477854000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>465681000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>455832000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>549081000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>487851100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>481677800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>470611500</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5158,8 +5478,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5241,8 +5563,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5324,8 +5652,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5407,8 +5741,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5490,91 +5830,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14008000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>14008000</v>
+      </c>
+      <c r="F72" s="3">
         <v>14086000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>14086000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>12052000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>12052000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>11906000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>11906000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>10650000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>10650000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>11928000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>11928000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>11325000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>11325000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>10653000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>14424000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>13420000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>13575000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>22597000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>21817000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>12954000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>12326000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>11700000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>10942000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>13160800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>13611800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>12624100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>11572000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5656,8 +6008,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5739,8 +6097,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5822,91 +6186,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19803000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>19803000</v>
+      </c>
+      <c r="F76" s="3">
         <v>20117000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>20117000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>18119000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>18119000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>17492000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>17492000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>16171000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>16171000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>17823000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>17823000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>17159000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>17159000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>16731000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>20878000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>19110000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>19477000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>25037000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>21968000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>15882000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>16087000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>15449000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>14666000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>18881500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>16897300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>15938400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>15552600</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5988,179 +6364,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>477000</v>
+      </c>
+      <c r="F81" s="3">
         <v>1347000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1347000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>642000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>642000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1082500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1082500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>60000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>60000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>378500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>378500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>472000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>472000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>250500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1606000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>512000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1204000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2632000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>4019000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1355000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>884000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1505000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>888200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1488200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1893500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6190,56 +6584,58 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>67000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>67000</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>154000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>72500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>72500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>72500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3">
         <v>42000</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -6273,8 +6669,14 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6356,8 +6758,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6439,8 +6847,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6522,8 +6936,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6605,8 +7025,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6688,91 +7114,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F89" s="3">
         <v>841500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>841500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>383500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>383500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>718000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>718000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1086500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1086500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-217500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-217500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>633500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>633500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-319000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>325000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2109000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-5016000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-746000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2745000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>980000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1530000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>90000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1398000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1038100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>174800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>3159000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1638100</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6802,91 +7240,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-28500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-28500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-23500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-23500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-37000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-37000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-13500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-13500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-13000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-13000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-9000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-9000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-14000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-43000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-43000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-16000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-100000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-59000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-78000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-316000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-41400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-216500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-118500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-160600</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6968,8 +7414,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7051,91 +7503,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-115500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-115500</v>
+      </c>
+      <c r="F94" s="3">
         <v>691000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>691000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-147000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-147000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-281000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-281000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-135000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-135000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-209000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-209000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>29000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>29000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>12500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-417000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-776000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-236000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-88000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-431000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-191000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>59000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>757000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-215000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-431800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-538700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-73700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7165,91 +7629,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>199500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>199500</v>
+      </c>
+      <c r="F96" s="3">
         <v>84000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>84000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>213000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>213000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>81000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>81000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>195000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>195000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>86000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>86000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>180500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>180500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>77000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-140000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-674000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-764000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-870000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-1244000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-840000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-373000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-786000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-332000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-410900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-867800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-375300</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7331,8 +7803,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7414,8 +7892,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7497,253 +7981,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-780000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-780000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-468500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-468500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-403500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-403500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-562000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-562000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-285500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-285500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-165500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-165500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-439500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-439500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-146500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>67000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>145000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1183000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1274000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>214000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-680000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-715000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-987000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>41000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-532600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-598700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-283100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1173300</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F101" s="3">
         <v>22000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>22000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-52500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-52500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>7500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>7500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-20000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-20000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>2500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-90000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-90000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>129000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-59000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>193000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>10000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>304000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>31000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-77000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>311000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>893300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>289600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-314700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>150100</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-908500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-908500</v>
+      </c>
+      <c r="F102" s="3">
         <v>1035000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1035000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-68000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-68000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-103000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-103000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>613500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>613500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-584500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-584500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>203000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>203000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-450500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-366000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>1419000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-6184000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2293000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2547000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>140000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>797000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-172000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>1535000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>967000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-673000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>2487400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>666300</v>
       </c>
     </row>
